--- a/Data/Budgets_PEPR_FairCarboN.xlsx
+++ b/Data/Budgets_PEPR_FairCarboN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2FC54A-A25D-4887-AF81-1B082BEE752B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168E3631-5C8E-4CB4-B502-B6678B641654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{38CB9908-9B0F-4ADA-AF47-34EE6D7F408E}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>Budget</t>
   </si>
   <si>
-    <t>FairCarboN</t>
-  </si>
-  <si>
     <t>ALAMOD</t>
   </si>
   <si>
@@ -103,6 +100,9 @@
   </si>
   <si>
     <t>Gouvernance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -524,10 +524,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="3">
         <v>7</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3">
         <v>6.5</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
         <v>2.8</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3">
         <v>1.5</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3">
         <v>2</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3">
         <v>1.5</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3">
         <v>1.494</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3">
         <v>1.399</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3">
         <v>1.488</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3">
         <v>1.496</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3">
         <v>1.4850000000000001</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3">
         <v>1.25</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3">
         <v>1.25</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3">
         <v>1.244</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3">
         <v>1.25</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3">
         <v>1.1000000000000001</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="3">
         <v>5.2</v>

--- a/Data/Budgets_PEPR_FairCarboN.xlsx
+++ b/Data/Budgets_PEPR_FairCarboN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168E3631-5C8E-4CB4-B502-B6678B641654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FF3EF8-357A-4CF8-9146-6444EA744147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{38CB9908-9B0F-4ADA-AF47-34EE6D7F408E}"/>
   </bookViews>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="3">
-        <v>1.494</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -607,7 +607,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="3">
-        <v>1.399</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -618,7 +618,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="3">
-        <v>1.488</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -629,7 +629,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="3">
-        <v>1.496</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -640,7 +640,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="3">
-        <v>1.4850000000000001</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -651,7 +651,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="3">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -662,7 +662,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="3">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -673,7 +673,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="3">
-        <v>1.244</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -684,7 +684,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="3">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
